--- a/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/Tables/Signals_Summary_Stats_Full_GDP_AR2.xlsx
+++ b/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/Tables/Signals_Summary_Stats_Full_GDP_AR2.xlsx
@@ -476,7 +476,7 @@
         <v>0.07167131012409561</v>
       </c>
       <c r="C3">
-        <v>0.3862527602944517</v>
+        <v>0.08030554661355933</v>
       </c>
       <c r="D3">
         <v>0.2271574986030922</v>
@@ -485,10 +485,10 @@
         <v>0.0962595149502147</v>
       </c>
       <c r="F3">
-        <v>-0.1590952616913596</v>
+        <v>0.1468519519895328</v>
       </c>
       <c r="G3">
-        <v>-0.289993245344237</v>
+        <v>0.01595396833665537</v>
       </c>
       <c r="H3">
         <v>-0.02458820482611912</v>
@@ -502,7 +502,7 @@
         <v>2.023371289315851</v>
       </c>
       <c r="C4">
-        <v>0.4697910137454391</v>
+        <v>1.359223760015442</v>
       </c>
       <c r="D4">
         <v>1.566344996427581</v>
@@ -511,10 +511,10 @@
         <v>2.084792614420148</v>
       </c>
       <c r="F4">
-        <v>1.767741064500687</v>
+        <v>2.421337893589921</v>
       </c>
       <c r="G4">
-        <v>2.249866418122989</v>
+        <v>2.773230669838306</v>
       </c>
       <c r="H4">
         <v>0.6378777121662803</v>
@@ -528,7 +528,7 @@
         <v>-9.690957649751999</v>
       </c>
       <c r="C5">
-        <v>-1.982134026001563</v>
+        <v>-7.463655357282573</v>
       </c>
       <c r="D5">
         <v>-7.451780981</v>
@@ -537,10 +537,10 @@
         <v>-11.9</v>
       </c>
       <c r="F5">
-        <v>-7.638046598226659</v>
+        <v>-6.767209248080064</v>
       </c>
       <c r="G5">
-        <v>-12.08626561722666</v>
+        <v>-11.21542826708007</v>
       </c>
       <c r="H5">
         <v>-2.3218073188947</v>
@@ -554,7 +554,7 @@
         <v>-0.1766203880255088</v>
       </c>
       <c r="C6">
-        <v>0.4410177662127912</v>
+        <v>0.2090227013014192</v>
       </c>
       <c r="D6">
         <v>-0.1258812636614508</v>
@@ -563,10 +563,10 @@
         <v>-0.07367641165386374</v>
       </c>
       <c r="F6">
-        <v>-0.4684301723397076</v>
+        <v>-0.4412093827197598</v>
       </c>
       <c r="G6">
-        <v>-0.525235846043772</v>
+        <v>-0.3960911288850362</v>
       </c>
       <c r="H6">
         <v>-0.2706508082905715</v>
@@ -580,7 +580,7 @@
         <v>0.1294760796771149</v>
       </c>
       <c r="C7">
-        <v>0.4877239970754673</v>
+        <v>0.3954517053573119</v>
       </c>
       <c r="D7">
         <v>0.2917081765</v>
@@ -589,10 +589,10 @@
         <v>0.2000000000000014</v>
       </c>
       <c r="F7">
-        <v>-0.1799249336813229</v>
+        <v>-0.1422074297624279</v>
       </c>
       <c r="G7">
-        <v>-0.2824380775195979</v>
+        <v>-0.1274799671716925</v>
       </c>
       <c r="H7">
         <v>-0.06777388263282783</v>
@@ -606,7 +606,7 @@
         <v>0.4115750142248751</v>
       </c>
       <c r="C8">
-        <v>0.5282525529321059</v>
+        <v>0.5001221795316644</v>
       </c>
       <c r="D8">
         <v>0.5306859673368906</v>
@@ -615,10 +615,10 @@
         <v>0.4614641609327548</v>
       </c>
       <c r="F8">
-        <v>0.009152774324852814</v>
+        <v>0.2172592321328845</v>
       </c>
       <c r="G8">
-        <v>0.008809470118964421</v>
+        <v>0.1481820764912898</v>
       </c>
       <c r="H8">
         <v>0.1718596188344542</v>
@@ -632,7 +632,7 @@
         <v>8.48030415038547</v>
       </c>
       <c r="C9">
-        <v>0.731431855473491</v>
+        <v>0.892999978012982</v>
       </c>
       <c r="D9">
         <v>6.405694238</v>
@@ -641,10 +641,10 @@
         <v>6.640000000000001</v>
       </c>
       <c r="F9">
-        <v>8.387828264001563</v>
+        <v>13.86934959528257</v>
       </c>
       <c r="G9">
-        <v>8.622134026001564</v>
+        <v>14.10365535728257</v>
       </c>
       <c r="H9">
         <v>2.209042350248001</v>
